--- a/backend/data/financials_by_company/1268.HK.xlsx
+++ b/backend/data/financials_by_company/1268.HK.xlsx
@@ -677,610 +677,610 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-404652843.143544</v>
+        <v>51767428.772237</v>
       </c>
       <c r="C2" t="n">
-        <v>0.142601</v>
+        <v>0.247664</v>
       </c>
       <c r="D2" t="n">
-        <v>-1913796000</v>
+        <v>1824370000</v>
       </c>
       <c r="E2" t="n">
-        <v>73296000</v>
+        <v>209023000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2837656000</v>
+        <v>209023000</v>
       </c>
       <c r="G2" t="n">
-        <v>-2264060000</v>
+        <v>1165640000</v>
       </c>
       <c r="H2" t="n">
-        <v>554692000</v>
+        <v>287353000</v>
       </c>
       <c r="I2" t="n">
-        <v>20592921000</v>
+        <v>20806155000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1840500000</v>
+        <v>2033393000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2395192000</v>
+        <v>1746040000</v>
       </c>
       <c r="L2" t="n">
-        <v>-135360000</v>
+        <v>-112317000</v>
       </c>
       <c r="M2" t="n">
-        <v>239325000</v>
+        <v>133277000</v>
       </c>
       <c r="N2" t="n">
-        <v>103965000</v>
+        <v>20960000</v>
       </c>
       <c r="O2" t="n">
-        <v>3079895156.856456</v>
+        <v>1008384428.772237</v>
       </c>
       <c r="P2" t="n">
-        <v>-2264060000</v>
+        <v>1165640000</v>
       </c>
       <c r="Q2" t="n">
-        <v>21836626000</v>
+        <v>22117359000</v>
       </c>
       <c r="R2" t="n">
-        <v>-2412684000</v>
+        <v>1698021000</v>
       </c>
       <c r="S2" t="n">
-        <v>1346247000</v>
+        <v>1261760000</v>
       </c>
       <c r="T2" t="n">
-        <v>1346247000</v>
+        <v>1245142000</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6818</v>
+        <v>0.9238</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6818</v>
+        <v>0.9362</v>
       </c>
       <c r="W2" t="n">
-        <v>-2264060000</v>
+        <v>1165640000</v>
       </c>
       <c r="X2" t="n">
-        <v>-2264060000</v>
+        <v>1165640000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2264060000</v>
+        <v>1165640000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-5228000</v>
+        <v>-47700000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2258832000</v>
+        <v>1213340000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2258832000</v>
+        <v>1213340000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-375685000</v>
+        <v>399423000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2634517000</v>
+        <v>1612763000</v>
       </c>
       <c r="AF2" t="n">
-        <v>25275000</v>
+        <v>28905000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2837656000</v>
+        <v>209023000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-73296000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-179309000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-29714000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-135360000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-112317000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>10665000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>239325000</v>
+        <v>133277000</v>
       </c>
       <c r="AM2" t="n">
-        <v>103965000</v>
+        <v>20960000</v>
       </c>
       <c r="AN2" t="n">
-        <v>317326000</v>
+        <v>1459330000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1243705000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>1311204000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18802000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18802000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>1246745000</v>
+        <v>1300715000</v>
       </c>
       <c r="AT2" t="n">
-        <v>584698000</v>
+        <v>741039000</v>
       </c>
       <c r="AU2" t="n">
-        <v>662047000</v>
+        <v>559676000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1561031000</v>
+        <v>2770534000</v>
       </c>
       <c r="AW2" t="n">
-        <v>20592921000</v>
+        <v>20806155000</v>
       </c>
       <c r="AX2" t="n">
-        <v>22153952000</v>
+        <v>23576689000</v>
       </c>
       <c r="AY2" t="n">
-        <v>22153952000</v>
+        <v>23576689000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>11962250</v>
+        <v>70862124.427357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.356213</v>
       </c>
       <c r="D3" t="n">
-        <v>1143402000</v>
+        <v>1429676000</v>
       </c>
       <c r="E3" t="n">
-        <v>109405000</v>
+        <v>198932000</v>
       </c>
       <c r="F3" t="n">
-        <v>47849000</v>
+        <v>198932000</v>
       </c>
       <c r="G3" t="n">
-        <v>140203000</v>
+        <v>521029000</v>
       </c>
       <c r="H3" t="n">
-        <v>577171000</v>
+        <v>490029000</v>
       </c>
       <c r="I3" t="n">
-        <v>26476606000</v>
+        <v>26137264000</v>
       </c>
       <c r="J3" t="n">
-        <v>1252807000</v>
+        <v>1628608000</v>
       </c>
       <c r="K3" t="n">
-        <v>675636000</v>
+        <v>1138579000</v>
       </c>
       <c r="L3" t="n">
-        <v>-182544000</v>
+        <v>-228924000</v>
       </c>
       <c r="M3" t="n">
-        <v>291162000</v>
+        <v>275039000</v>
       </c>
       <c r="N3" t="n">
-        <v>108618000</v>
+        <v>46115000</v>
       </c>
       <c r="O3" t="n">
-        <v>165872250</v>
+        <v>392959124.427357</v>
       </c>
       <c r="P3" t="n">
-        <v>140203000</v>
+        <v>521029000</v>
       </c>
       <c r="Q3" t="n">
-        <v>28078833000</v>
+        <v>27798251000</v>
       </c>
       <c r="R3" t="n">
-        <v>655180000</v>
+        <v>1113644000</v>
       </c>
       <c r="S3" t="n">
-        <v>1346497000</v>
+        <v>1282953000</v>
       </c>
       <c r="T3" t="n">
-        <v>1342764000</v>
+        <v>1273120000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1041</v>
+        <v>0.4061</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1044</v>
+        <v>0.4093</v>
       </c>
       <c r="W3" t="n">
-        <v>140203000</v>
+        <v>521029000</v>
       </c>
       <c r="X3" t="n">
-        <v>140203000</v>
+        <v>521029000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>140203000</v>
+        <v>521029000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-15577000</v>
+        <v>-34907000</v>
       </c>
       <c r="AB3" t="n">
-        <v>155780000</v>
+        <v>555936000</v>
       </c>
       <c r="AC3" t="n">
-        <v>155780000</v>
+        <v>555936000</v>
       </c>
       <c r="AD3" t="n">
-        <v>228694000</v>
+        <v>307604000</v>
       </c>
       <c r="AE3" t="n">
-        <v>384474000</v>
+        <v>863540000</v>
       </c>
       <c r="AF3" t="n">
-        <v>24805000</v>
+        <v>28359000</v>
       </c>
       <c r="AG3" t="n">
-        <v>47849000</v>
+        <v>198932000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-109405000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>-198932000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>-182544000</v>
+        <v>-228924000</v>
       </c>
       <c r="AK3" t="n">
-        <v>17106000</v>
+        <v>16241000</v>
       </c>
       <c r="AL3" t="n">
-        <v>291162000</v>
+        <v>275039000</v>
       </c>
       <c r="AM3" t="n">
-        <v>108618000</v>
+        <v>46115000</v>
       </c>
       <c r="AN3" t="n">
-        <v>475720000</v>
+        <v>856483000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1602227000</v>
+        <v>1660987000</v>
       </c>
       <c r="AP3" t="n">
-        <v>182197000</v>
+        <v>131533000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>182197000</v>
+        <v>131533000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1610311000</v>
+        <v>1539109000</v>
       </c>
       <c r="AT3" t="n">
-        <v>763604000</v>
+        <v>859912000</v>
       </c>
       <c r="AU3" t="n">
-        <v>846707000</v>
+        <v>679197000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2077947000</v>
+        <v>2517470000</v>
       </c>
       <c r="AW3" t="n">
-        <v>26476606000</v>
+        <v>26137264000</v>
       </c>
       <c r="AX3" t="n">
-        <v>28554553000</v>
+        <v>28654734000</v>
       </c>
       <c r="AY3" t="n">
-        <v>28554553000</v>
+        <v>28654734000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>70862124.427357</v>
+        <v>11962250</v>
       </c>
       <c r="C4" t="n">
-        <v>0.356213</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1429676000</v>
+        <v>1143402000</v>
       </c>
       <c r="E4" t="n">
-        <v>198932000</v>
+        <v>109405000</v>
       </c>
       <c r="F4" t="n">
-        <v>198932000</v>
+        <v>47849000</v>
       </c>
       <c r="G4" t="n">
-        <v>521029000</v>
+        <v>140203000</v>
       </c>
       <c r="H4" t="n">
-        <v>490029000</v>
+        <v>577171000</v>
       </c>
       <c r="I4" t="n">
-        <v>26137264000</v>
+        <v>26476606000</v>
       </c>
       <c r="J4" t="n">
-        <v>1628608000</v>
+        <v>1252807000</v>
       </c>
       <c r="K4" t="n">
-        <v>1138579000</v>
+        <v>675636000</v>
       </c>
       <c r="L4" t="n">
-        <v>-228924000</v>
+        <v>-182544000</v>
       </c>
       <c r="M4" t="n">
-        <v>275039000</v>
+        <v>291162000</v>
       </c>
       <c r="N4" t="n">
-        <v>46115000</v>
+        <v>108618000</v>
       </c>
       <c r="O4" t="n">
-        <v>392959124.427357</v>
+        <v>165872250</v>
       </c>
       <c r="P4" t="n">
-        <v>521029000</v>
+        <v>140203000</v>
       </c>
       <c r="Q4" t="n">
-        <v>27798251000</v>
+        <v>28078833000</v>
       </c>
       <c r="R4" t="n">
-        <v>1113644000</v>
+        <v>655180000</v>
       </c>
       <c r="S4" t="n">
-        <v>1282953000</v>
+        <v>1346497000</v>
       </c>
       <c r="T4" t="n">
-        <v>1273120000</v>
+        <v>1342764000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4061</v>
+        <v>0.1041</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4093</v>
+        <v>0.1044</v>
       </c>
       <c r="W4" t="n">
-        <v>521029000</v>
+        <v>140203000</v>
       </c>
       <c r="X4" t="n">
-        <v>521029000</v>
+        <v>140203000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>521029000</v>
+        <v>140203000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-34907000</v>
+        <v>-15577000</v>
       </c>
       <c r="AB4" t="n">
-        <v>555936000</v>
+        <v>155780000</v>
       </c>
       <c r="AC4" t="n">
-        <v>555936000</v>
+        <v>155780000</v>
       </c>
       <c r="AD4" t="n">
-        <v>307604000</v>
+        <v>228694000</v>
       </c>
       <c r="AE4" t="n">
-        <v>863540000</v>
+        <v>384474000</v>
       </c>
       <c r="AF4" t="n">
-        <v>28359000</v>
+        <v>24805000</v>
       </c>
       <c r="AG4" t="n">
-        <v>198932000</v>
+        <v>47849000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-198932000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>-109405000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-228924000</v>
+        <v>-182544000</v>
       </c>
       <c r="AK4" t="n">
-        <v>16241000</v>
+        <v>17106000</v>
       </c>
       <c r="AL4" t="n">
-        <v>275039000</v>
+        <v>291162000</v>
       </c>
       <c r="AM4" t="n">
-        <v>46115000</v>
+        <v>108618000</v>
       </c>
       <c r="AN4" t="n">
-        <v>856483000</v>
+        <v>475720000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1660987000</v>
+        <v>1602227000</v>
       </c>
       <c r="AP4" t="n">
-        <v>131533000</v>
+        <v>182197000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>131533000</v>
+        <v>182197000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1539109000</v>
+        <v>1610311000</v>
       </c>
       <c r="AT4" t="n">
-        <v>859912000</v>
+        <v>763604000</v>
       </c>
       <c r="AU4" t="n">
-        <v>679197000</v>
+        <v>846707000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2517470000</v>
+        <v>2077947000</v>
       </c>
       <c r="AW4" t="n">
-        <v>26137264000</v>
+        <v>26476606000</v>
       </c>
       <c r="AX4" t="n">
-        <v>28654734000</v>
+        <v>28554553000</v>
       </c>
       <c r="AY4" t="n">
-        <v>28654734000</v>
+        <v>28554553000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>51767428.772237</v>
+        <v>-404652843.143544</v>
       </c>
       <c r="C5" t="n">
-        <v>0.247664</v>
+        <v>0.142601</v>
       </c>
       <c r="D5" t="n">
-        <v>1824370000</v>
+        <v>-1913796000</v>
       </c>
       <c r="E5" t="n">
-        <v>209023000</v>
+        <v>73296000</v>
       </c>
       <c r="F5" t="n">
-        <v>209023000</v>
+        <v>-2837656000</v>
       </c>
       <c r="G5" t="n">
-        <v>1165640000</v>
+        <v>-2264060000</v>
       </c>
       <c r="H5" t="n">
-        <v>287353000</v>
+        <v>554692000</v>
       </c>
       <c r="I5" t="n">
-        <v>20806155000</v>
+        <v>20592921000</v>
       </c>
       <c r="J5" t="n">
-        <v>2033393000</v>
+        <v>-1840500000</v>
       </c>
       <c r="K5" t="n">
-        <v>1746040000</v>
+        <v>-2395192000</v>
       </c>
       <c r="L5" t="n">
-        <v>-112317000</v>
+        <v>-135360000</v>
       </c>
       <c r="M5" t="n">
-        <v>133277000</v>
+        <v>239325000</v>
       </c>
       <c r="N5" t="n">
-        <v>20960000</v>
+        <v>103965000</v>
       </c>
       <c r="O5" t="n">
-        <v>1008384428.772237</v>
+        <v>3079895156.856456</v>
       </c>
       <c r="P5" t="n">
-        <v>1165640000</v>
+        <v>-2264060000</v>
       </c>
       <c r="Q5" t="n">
-        <v>22117359000</v>
+        <v>21836626000</v>
       </c>
       <c r="R5" t="n">
-        <v>1698021000</v>
+        <v>-2412684000</v>
       </c>
       <c r="S5" t="n">
-        <v>1261760000</v>
+        <v>1346247000</v>
       </c>
       <c r="T5" t="n">
-        <v>1245142000</v>
+        <v>1346247000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9238</v>
+        <v>-1.6818</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9362</v>
+        <v>-1.6818</v>
       </c>
       <c r="W5" t="n">
-        <v>1165640000</v>
+        <v>-2264060000</v>
       </c>
       <c r="X5" t="n">
-        <v>1165640000</v>
+        <v>-2264060000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1165640000</v>
+        <v>-2264060000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-47700000</v>
+        <v>-5228000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1213340000</v>
+        <v>-2258832000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1213340000</v>
+        <v>-2258832000</v>
       </c>
       <c r="AD5" t="n">
-        <v>399423000</v>
+        <v>-375685000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1612763000</v>
+        <v>-2634517000</v>
       </c>
       <c r="AF5" t="n">
-        <v>28905000</v>
+        <v>25275000</v>
       </c>
       <c r="AG5" t="n">
-        <v>209023000</v>
+        <v>-2837656000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-179309000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-29714000</v>
-      </c>
+        <v>-73296000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-112317000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>10665000</v>
-      </c>
+        <v>-135360000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>133277000</v>
+        <v>239325000</v>
       </c>
       <c r="AM5" t="n">
-        <v>20960000</v>
+        <v>103965000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1459330000</v>
+        <v>317326000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1311204000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>18802000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>18802000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>1243705000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>1300715000</v>
+        <v>1246745000</v>
       </c>
       <c r="AT5" t="n">
-        <v>741039000</v>
+        <v>584698000</v>
       </c>
       <c r="AU5" t="n">
-        <v>559676000</v>
+        <v>662047000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2770534000</v>
+        <v>1561031000</v>
       </c>
       <c r="AW5" t="n">
-        <v>20806155000</v>
+        <v>20592921000</v>
       </c>
       <c r="AX5" t="n">
-        <v>23576689000</v>
+        <v>22153952000</v>
       </c>
       <c r="AY5" t="n">
-        <v>23576689000</v>
+        <v>22153952000</v>
       </c>
     </row>
   </sheetData>
@@ -1616,756 +1616,756 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1346247201</v>
+        <v>1247867000</v>
       </c>
       <c r="C2" t="n">
-        <v>1346247201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>116116000</v>
-      </c>
+        <v>1247867000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>4081104000</v>
+        <v>2581271000</v>
       </c>
       <c r="F2" t="n">
-        <v>1221619000</v>
+        <v>2821828000</v>
       </c>
       <c r="G2" t="n">
-        <v>5594956000</v>
+        <v>5235502000</v>
       </c>
       <c r="H2" t="n">
-        <v>324673000</v>
+        <v>1473670000</v>
       </c>
       <c r="I2" t="n">
-        <v>1221619000</v>
+        <v>2821828000</v>
       </c>
       <c r="J2" t="n">
-        <v>1320449000</v>
+        <v>1292393000</v>
       </c>
       <c r="K2" t="n">
-        <v>2834301000</v>
+        <v>3946624000</v>
       </c>
       <c r="L2" t="n">
-        <v>3126001000</v>
+        <v>4246012000</v>
       </c>
       <c r="M2" t="n">
-        <v>2956783000</v>
+        <v>4116593000</v>
       </c>
       <c r="N2" t="n">
-        <v>122482000</v>
+        <v>169969000</v>
       </c>
       <c r="O2" t="n">
-        <v>2834301000</v>
+        <v>3946624000</v>
       </c>
       <c r="P2" t="n">
-        <v>1435050000</v>
+        <v>3145146000</v>
       </c>
       <c r="Q2" t="n">
-        <v>670877000</v>
+        <v>345540000</v>
       </c>
       <c r="R2" t="n">
-        <v>107888000</v>
+        <v>99520000</v>
       </c>
       <c r="S2" t="n">
-        <v>107888000</v>
+        <v>99520000</v>
       </c>
       <c r="T2" t="n">
-        <v>8524532000</v>
+        <v>5686080000</v>
       </c>
       <c r="U2" t="n">
-        <v>1736138000</v>
+        <v>1596630000</v>
       </c>
       <c r="V2" t="n">
-        <v>293905000</v>
+        <v>137270000</v>
       </c>
       <c r="W2" t="n">
-        <v>1442233000</v>
+        <v>1459360000</v>
       </c>
       <c r="X2" t="n">
-        <v>1150533000</v>
+        <v>1159972000</v>
       </c>
       <c r="Y2" t="n">
-        <v>291700000</v>
+        <v>299388000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6788394000</v>
+        <v>4089450000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2638871000</v>
+        <v>1121911000</v>
       </c>
       <c r="AB2" t="n">
-        <v>169916000</v>
+        <v>132421000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2468955000</v>
+        <v>989490000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3428519000</v>
+        <v>2256439000</v>
       </c>
       <c r="AE2" t="n">
-        <v>295669000</v>
+        <v>407218000</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>93065000</v>
+        <v>179941000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3039785000</v>
+        <v>1669280000</v>
       </c>
       <c r="AI2" t="n">
-        <v>11481315000</v>
+        <v>9802673000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4368248000</v>
+        <v>4239553000</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>58696000</v>
+        <v>416922000</v>
       </c>
       <c r="AM2" t="n">
-        <v>136133000</v>
+        <v>80459000</v>
       </c>
       <c r="AN2" t="n">
-        <v>32803000</v>
+        <v>61942000</v>
       </c>
       <c r="AO2" t="n">
-        <v>32803000</v>
+        <v>61942000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1612682000</v>
+        <v>1124796000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1595155000</v>
+        <v>946105000</v>
       </c>
       <c r="AR2" t="n">
-        <v>17527000</v>
+        <v>178691000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2527934000</v>
+        <v>2555434000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1537908000</v>
+        <v>-766157000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4065842000</v>
+        <v>3321591000</v>
       </c>
       <c r="AV2" t="n">
-        <v>18974000</v>
+        <v>16484000</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>766888000</v>
+        <v>693908000</v>
       </c>
       <c r="AY2" t="n">
-        <v>3279980000</v>
+        <v>2611199000</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7113067000</v>
+        <v>5563120000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2108108000</v>
+        <v>768964000</v>
       </c>
       <c r="BC2" t="n">
-        <v>290147000</v>
+        <v>921918000</v>
       </c>
       <c r="BD2" t="n">
-        <v>760711000</v>
+        <v>355256000</v>
       </c>
       <c r="BE2" t="n">
-        <v>149876000</v>
+        <v>132403000</v>
       </c>
       <c r="BF2" t="n">
-        <v>610835000</v>
+        <v>222853000</v>
       </c>
       <c r="BG2" t="n">
-        <v>977724000</v>
+        <v>714011000</v>
       </c>
       <c r="BH2" t="n">
-        <v>319838000</v>
+        <v>181230000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2656539000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>12000000</v>
-      </c>
+        <v>2621741000</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="n">
-        <v>2644539000</v>
+        <v>2621741000</v>
       </c>
       <c r="BL2" t="n">
-        <v>2644539000</v>
+        <v>2621741000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1346247201</v>
+        <v>1276572364</v>
       </c>
       <c r="C3" t="n">
-        <v>1346247201</v>
+        <v>1276572364</v>
       </c>
       <c r="D3" t="n">
-        <v>1289549000</v>
+        <v>2546038000</v>
       </c>
       <c r="E3" t="n">
-        <v>5034834000</v>
+        <v>5637482000</v>
       </c>
       <c r="F3" t="n">
-        <v>433134000</v>
+        <v>-691234000</v>
       </c>
       <c r="G3" t="n">
-        <v>8803475000</v>
+        <v>8456689000</v>
       </c>
       <c r="H3" t="n">
-        <v>1925299000</v>
+        <v>1014741000</v>
       </c>
       <c r="I3" t="n">
-        <v>433134000</v>
+        <v>-691234000</v>
       </c>
       <c r="J3" t="n">
-        <v>1383614000</v>
+        <v>1455819000</v>
       </c>
       <c r="K3" t="n">
-        <v>5152255000</v>
+        <v>4275026000</v>
       </c>
       <c r="L3" t="n">
-        <v>7558536000</v>
+        <v>7042771000</v>
       </c>
       <c r="M3" t="n">
-        <v>5286140000</v>
+        <v>4433780000</v>
       </c>
       <c r="N3" t="n">
-        <v>133885000</v>
+        <v>158754000</v>
       </c>
       <c r="O3" t="n">
-        <v>5152255000</v>
+        <v>4275026000</v>
       </c>
       <c r="P3" t="n">
-        <v>3719830000</v>
+        <v>3614707000</v>
       </c>
       <c r="Q3" t="n">
-        <v>715303000</v>
+        <v>2473000</v>
       </c>
       <c r="R3" t="n">
-        <v>107888000</v>
+        <v>101888000</v>
       </c>
       <c r="S3" t="n">
-        <v>107888000</v>
+        <v>101888000</v>
       </c>
       <c r="T3" t="n">
-        <v>8934266000</v>
+        <v>9805623000</v>
       </c>
       <c r="U3" t="n">
-        <v>4486892000</v>
+        <v>4931887000</v>
       </c>
       <c r="V3" t="n">
-        <v>867393000</v>
+        <v>873518000</v>
       </c>
       <c r="W3" t="n">
-        <v>3619499000</v>
+        <v>4058369000</v>
       </c>
       <c r="X3" t="n">
-        <v>1213218000</v>
+        <v>1290624000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2406281000</v>
+        <v>2767745000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4447374000</v>
+        <v>4873736000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1415335000</v>
+        <v>1579113000</v>
       </c>
       <c r="AB3" t="n">
-        <v>170396000</v>
+        <v>165195000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1244939000</v>
+        <v>1413918000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2200963000</v>
+        <v>2274875000</v>
       </c>
       <c r="AE3" t="n">
-        <v>370093000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>334274000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="n">
-        <v>124990000</v>
+        <v>101751000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1705880000</v>
+        <v>1838850000</v>
       </c>
       <c r="AI3" t="n">
-        <v>14220406000</v>
+        <v>14239403000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7847733000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>8350926000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>74904000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>70236000</v>
+        <v>73519000</v>
       </c>
       <c r="AM3" t="n">
-        <v>133392000</v>
+        <v>126980000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36319000</v>
+        <v>38985000</v>
       </c>
       <c r="AO3" t="n">
-        <v>36319000</v>
+        <v>38985000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4719121000</v>
+        <v>4966260000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3758128000</v>
+        <v>3961748000</v>
       </c>
       <c r="AR3" t="n">
-        <v>960993000</v>
+        <v>1004512000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2888665000</v>
+        <v>3145182000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1262609000</v>
+        <v>-1002196000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4151274000</v>
+        <v>4147378000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4141000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>7278000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3628445000</v>
+      </c>
       <c r="AX3" t="n">
-        <v>856101000</v>
+        <v>830692000</v>
       </c>
       <c r="AY3" t="n">
-        <v>3291032000</v>
+        <v>3309408000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6372673000</v>
+        <v>5888477000</v>
       </c>
       <c r="BB3" t="n">
-        <v>971543000</v>
+        <v>910307000</v>
       </c>
       <c r="BC3" t="n">
-        <v>260061000</v>
+        <v>391125000</v>
       </c>
       <c r="BD3" t="n">
-        <v>960042000</v>
+        <v>1069360000</v>
       </c>
       <c r="BE3" t="n">
-        <v>191676000</v>
+        <v>186373000</v>
       </c>
       <c r="BF3" t="n">
-        <v>768366000</v>
+        <v>882987000</v>
       </c>
       <c r="BG3" t="n">
-        <v>981066000</v>
+        <v>890406000</v>
       </c>
       <c r="BH3" t="n">
-        <v>276385000</v>
+        <v>278958000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2923576000</v>
+        <v>2348321000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>561905000</v>
+        <v>712696000</v>
       </c>
       <c r="BK3" t="n">
-        <v>2361671000</v>
+        <v>1635625000</v>
       </c>
       <c r="BL3" t="n">
-        <v>2361671000</v>
+        <v>1635625000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1276572364</v>
+        <v>1346247201</v>
       </c>
       <c r="C4" t="n">
-        <v>1276572364</v>
+        <v>1346247201</v>
       </c>
       <c r="D4" t="n">
-        <v>2546038000</v>
+        <v>1289549000</v>
       </c>
       <c r="E4" t="n">
-        <v>5637482000</v>
+        <v>5034834000</v>
       </c>
       <c r="F4" t="n">
-        <v>-691234000</v>
+        <v>433134000</v>
       </c>
       <c r="G4" t="n">
-        <v>8456689000</v>
+        <v>8803475000</v>
       </c>
       <c r="H4" t="n">
-        <v>1014741000</v>
+        <v>1925299000</v>
       </c>
       <c r="I4" t="n">
-        <v>-691234000</v>
+        <v>433134000</v>
       </c>
       <c r="J4" t="n">
-        <v>1455819000</v>
+        <v>1383614000</v>
       </c>
       <c r="K4" t="n">
-        <v>4275026000</v>
+        <v>5152255000</v>
       </c>
       <c r="L4" t="n">
-        <v>7042771000</v>
+        <v>7558536000</v>
       </c>
       <c r="M4" t="n">
-        <v>4433780000</v>
+        <v>5286140000</v>
       </c>
       <c r="N4" t="n">
-        <v>158754000</v>
+        <v>133885000</v>
       </c>
       <c r="O4" t="n">
-        <v>4275026000</v>
+        <v>5152255000</v>
       </c>
       <c r="P4" t="n">
-        <v>3614707000</v>
+        <v>3719830000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2473000</v>
+        <v>715303000</v>
       </c>
       <c r="R4" t="n">
-        <v>101888000</v>
+        <v>107888000</v>
       </c>
       <c r="S4" t="n">
-        <v>101888000</v>
+        <v>107888000</v>
       </c>
       <c r="T4" t="n">
-        <v>9805623000</v>
+        <v>8934266000</v>
       </c>
       <c r="U4" t="n">
-        <v>4931887000</v>
+        <v>4486892000</v>
       </c>
       <c r="V4" t="n">
-        <v>873518000</v>
+        <v>867393000</v>
       </c>
       <c r="W4" t="n">
-        <v>4058369000</v>
+        <v>3619499000</v>
       </c>
       <c r="X4" t="n">
-        <v>1290624000</v>
+        <v>1213218000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2767745000</v>
+        <v>2406281000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4873736000</v>
+        <v>4447374000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1579113000</v>
+        <v>1415335000</v>
       </c>
       <c r="AB4" t="n">
-        <v>165195000</v>
+        <v>170396000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1413918000</v>
+        <v>1244939000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2274875000</v>
+        <v>2200963000</v>
       </c>
       <c r="AE4" t="n">
-        <v>334274000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
+        <v>370093000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>101751000</v>
+        <v>124990000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1838850000</v>
+        <v>1705880000</v>
       </c>
       <c r="AI4" t="n">
-        <v>14239403000</v>
+        <v>14220406000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8350926000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>74904000</v>
-      </c>
+        <v>7847733000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>73519000</v>
+        <v>70236000</v>
       </c>
       <c r="AM4" t="n">
-        <v>126980000</v>
+        <v>133392000</v>
       </c>
       <c r="AN4" t="n">
-        <v>38985000</v>
+        <v>36319000</v>
       </c>
       <c r="AO4" t="n">
-        <v>38985000</v>
+        <v>36319000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4966260000</v>
+        <v>4719121000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3961748000</v>
+        <v>3758128000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1004512000</v>
+        <v>960993000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3145182000</v>
+        <v>2888665000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1002196000</v>
+        <v>-1262609000</v>
       </c>
       <c r="AU4" t="n">
-        <v>4147378000</v>
+        <v>4151274000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7278000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3628445000</v>
-      </c>
+        <v>4141000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>830692000</v>
+        <v>856101000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3309408000</v>
+        <v>3291032000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>5888477000</v>
+        <v>6372673000</v>
       </c>
       <c r="BB4" t="n">
-        <v>910307000</v>
+        <v>971543000</v>
       </c>
       <c r="BC4" t="n">
-        <v>391125000</v>
+        <v>260061000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1069360000</v>
+        <v>960042000</v>
       </c>
       <c r="BE4" t="n">
-        <v>186373000</v>
+        <v>191676000</v>
       </c>
       <c r="BF4" t="n">
-        <v>882987000</v>
+        <v>768366000</v>
       </c>
       <c r="BG4" t="n">
-        <v>890406000</v>
+        <v>981066000</v>
       </c>
       <c r="BH4" t="n">
-        <v>278958000</v>
+        <v>276385000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2348321000</v>
+        <v>2923576000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>712696000</v>
+        <v>561905000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1635625000</v>
+        <v>2361671000</v>
       </c>
       <c r="BL4" t="n">
-        <v>1635625000</v>
+        <v>2361671000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1247867000</v>
+        <v>1346247201</v>
       </c>
       <c r="C5" t="n">
-        <v>1247867000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1346247201</v>
+      </c>
+      <c r="D5" t="n">
+        <v>116116000</v>
+      </c>
       <c r="E5" t="n">
-        <v>2581271000</v>
+        <v>4081104000</v>
       </c>
       <c r="F5" t="n">
-        <v>2821828000</v>
+        <v>1221619000</v>
       </c>
       <c r="G5" t="n">
-        <v>5235502000</v>
+        <v>5594956000</v>
       </c>
       <c r="H5" t="n">
-        <v>1473670000</v>
+        <v>324673000</v>
       </c>
       <c r="I5" t="n">
-        <v>2821828000</v>
+        <v>1221619000</v>
       </c>
       <c r="J5" t="n">
-        <v>1292393000</v>
+        <v>1320449000</v>
       </c>
       <c r="K5" t="n">
-        <v>3946624000</v>
+        <v>2834301000</v>
       </c>
       <c r="L5" t="n">
-        <v>4246012000</v>
+        <v>3126001000</v>
       </c>
       <c r="M5" t="n">
-        <v>4116593000</v>
+        <v>2956783000</v>
       </c>
       <c r="N5" t="n">
-        <v>169969000</v>
+        <v>122482000</v>
       </c>
       <c r="O5" t="n">
-        <v>3946624000</v>
+        <v>2834301000</v>
       </c>
       <c r="P5" t="n">
-        <v>3145146000</v>
+        <v>1435050000</v>
       </c>
       <c r="Q5" t="n">
-        <v>345540000</v>
+        <v>670877000</v>
       </c>
       <c r="R5" t="n">
-        <v>99520000</v>
+        <v>107888000</v>
       </c>
       <c r="S5" t="n">
-        <v>99520000</v>
+        <v>107888000</v>
       </c>
       <c r="T5" t="n">
-        <v>5686080000</v>
+        <v>8524532000</v>
       </c>
       <c r="U5" t="n">
-        <v>1596630000</v>
+        <v>1736138000</v>
       </c>
       <c r="V5" t="n">
-        <v>137270000</v>
+        <v>293905000</v>
       </c>
       <c r="W5" t="n">
-        <v>1459360000</v>
+        <v>1442233000</v>
       </c>
       <c r="X5" t="n">
-        <v>1159972000</v>
+        <v>1150533000</v>
       </c>
       <c r="Y5" t="n">
-        <v>299388000</v>
+        <v>291700000</v>
       </c>
       <c r="Z5" t="n">
-        <v>4089450000</v>
+        <v>6788394000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1121911000</v>
+        <v>2638871000</v>
       </c>
       <c r="AB5" t="n">
-        <v>132421000</v>
+        <v>169916000</v>
       </c>
       <c r="AC5" t="n">
-        <v>989490000</v>
+        <v>2468955000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2256439000</v>
+        <v>3428519000</v>
       </c>
       <c r="AE5" t="n">
-        <v>407218000</v>
+        <v>295669000</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>179941000</v>
+        <v>93065000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1669280000</v>
+        <v>3039785000</v>
       </c>
       <c r="AI5" t="n">
-        <v>9802673000</v>
+        <v>11481315000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4239553000</v>
+        <v>4368248000</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>416922000</v>
+        <v>58696000</v>
       </c>
       <c r="AM5" t="n">
-        <v>80459000</v>
+        <v>136133000</v>
       </c>
       <c r="AN5" t="n">
-        <v>61942000</v>
+        <v>32803000</v>
       </c>
       <c r="AO5" t="n">
-        <v>61942000</v>
+        <v>32803000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1124796000</v>
+        <v>1612682000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>946105000</v>
+        <v>1595155000</v>
       </c>
       <c r="AR5" t="n">
-        <v>178691000</v>
+        <v>17527000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2555434000</v>
+        <v>2527934000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-766157000</v>
+        <v>-1537908000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3321591000</v>
+        <v>4065842000</v>
       </c>
       <c r="AV5" t="n">
-        <v>16484000</v>
+        <v>18974000</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>693908000</v>
+        <v>766888000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2611199000</v>
+        <v>3279980000</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>5563120000</v>
+        <v>7113067000</v>
       </c>
       <c r="BB5" t="n">
-        <v>768964000</v>
+        <v>2108108000</v>
       </c>
       <c r="BC5" t="n">
-        <v>921918000</v>
+        <v>290147000</v>
       </c>
       <c r="BD5" t="n">
-        <v>355256000</v>
+        <v>760711000</v>
       </c>
       <c r="BE5" t="n">
-        <v>132403000</v>
+        <v>149876000</v>
       </c>
       <c r="BF5" t="n">
-        <v>222853000</v>
+        <v>610835000</v>
       </c>
       <c r="BG5" t="n">
-        <v>714011000</v>
+        <v>977724000</v>
       </c>
       <c r="BH5" t="n">
-        <v>181230000</v>
+        <v>319838000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2621741000</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
+        <v>2656539000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12000000</v>
+      </c>
       <c r="BK5" t="n">
-        <v>2621741000</v>
+        <v>2644539000</v>
       </c>
       <c r="BL5" t="n">
-        <v>2621741000</v>
+        <v>2644539000</v>
       </c>
     </row>
   </sheetData>
@@ -2621,570 +2621,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>753744000</v>
+        <v>1449063000</v>
       </c>
       <c r="C2" t="n">
-        <v>-8631529000</v>
+        <v>-8166627000</v>
       </c>
       <c r="D2" t="n">
-        <v>7603056000</v>
+        <v>8483368000</v>
       </c>
       <c r="E2" t="n">
+        <v>11104000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-362858000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2621741000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2538030000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-28658000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>112369000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-317494000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16787000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-133250000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-460916000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-460916000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11104000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11104000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>316741000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>316741000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-8166627000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8483368000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1382058000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-618379000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>21363000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>42425000</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>-110911000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2644539000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2361671000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-78000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>282946000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-1312183000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6532000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-149051000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-44426000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-44426000</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1028473000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-1028473000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-8631529000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>7603056000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>730474000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>131839000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>21008000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>549905000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>549905000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>-613335000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-613335000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>27722000</v>
+        <v>-214132000</v>
       </c>
       <c r="AF2" t="n">
-        <v>138633000</v>
+        <v>148726000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-110911000</v>
+        <v>-362858000</v>
       </c>
       <c r="AH2" t="n">
-        <v>864655000</v>
+        <v>1811921000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-232469000</v>
+        <v>-377848000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>106076000</v>
+        <v>276278000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1130826000</v>
+        <v>-207483000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1183912000</v>
+        <v>513420000</v>
       </c>
       <c r="AM2" t="n">
-        <v>157274000</v>
+        <v>190700000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-104284000</v>
+        <v>-220359000</v>
       </c>
       <c r="AO2" t="n">
-        <v>124133000</v>
+        <v>82603000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5892000</v>
+        <v>4130000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>554692000</v>
+        <v>287353000</v>
       </c>
       <c r="AR2" t="n">
-        <v>179607000</v>
+        <v>18802000</v>
       </c>
       <c r="AS2" t="n">
-        <v>375085000</v>
+        <v>268551000</v>
       </c>
       <c r="AT2" t="n">
-        <v>78000</v>
+        <v>22310000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5253000</v>
+        <v>-47649000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2634517000</v>
+        <v>1612763000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>469057000</v>
+        <v>870430000</v>
       </c>
       <c r="C3" t="n">
-        <v>-14446154000</v>
+        <v>-13100444000</v>
       </c>
       <c r="D3" t="n">
-        <v>13789609000</v>
+        <v>15060069000</v>
       </c>
       <c r="E3" t="n">
-        <v>876660000</v>
+        <v>647230000</v>
       </c>
       <c r="F3" t="n">
-        <v>-347730000</v>
+        <v>-283391000</v>
       </c>
       <c r="G3" t="n">
-        <v>2361671000</v>
+        <v>1635625000</v>
       </c>
       <c r="H3" t="n">
-        <v>1635625000</v>
+        <v>2621741000</v>
       </c>
       <c r="I3" t="n">
-        <v>2751000</v>
+        <v>15739000</v>
       </c>
       <c r="J3" t="n">
-        <v>723295000</v>
+        <v>-1001855000</v>
       </c>
       <c r="K3" t="n">
-        <v>-250293000</v>
+        <v>1327784000</v>
       </c>
       <c r="L3" t="n">
-        <v>1442000</v>
+        <v>557000</v>
       </c>
       <c r="M3" t="n">
-        <v>-181781000</v>
+        <v>-177463000</v>
       </c>
       <c r="N3" t="n">
-        <v>-169223000</v>
+        <v>-994706000</v>
       </c>
       <c r="O3" t="n">
-        <v>-169223000</v>
+        <v>-994706000</v>
       </c>
       <c r="P3" t="n">
-        <v>876660000</v>
+        <v>647230000</v>
       </c>
       <c r="Q3" t="n">
-        <v>876660000</v>
+        <v>647230000</v>
       </c>
       <c r="R3" t="n">
-        <v>-656545000</v>
+        <v>1959625000</v>
       </c>
       <c r="S3" t="n">
-        <v>-656545000</v>
+        <v>1959625000</v>
       </c>
       <c r="T3" t="n">
-        <v>-14446154000</v>
+        <v>-13100444000</v>
       </c>
       <c r="U3" t="n">
-        <v>13789609000</v>
+        <v>15060069000</v>
       </c>
       <c r="V3" t="n">
-        <v>156801000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>-3483460000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-31265000</v>
+      </c>
       <c r="X3" t="n">
-        <v>86356000</v>
+        <v>40054000</v>
       </c>
       <c r="Y3" t="n">
-        <v>23122000</v>
+        <v>47892000</v>
       </c>
       <c r="Z3" t="n">
-        <v>150791000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>150791000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>-712696000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>-712696000</v>
+      </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-2701463000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2701463000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-103468000</v>
+        <v>-125982000</v>
       </c>
       <c r="AF3" t="n">
-        <v>244262000</v>
+        <v>157409000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-347730000</v>
+        <v>-283391000</v>
       </c>
       <c r="AH3" t="n">
-        <v>816787000</v>
+        <v>1153821000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-217992000</v>
+        <v>-472191000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-139164000</v>
+        <v>67078000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-47710000</v>
+        <v>-166039000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-247938000</v>
+        <v>-48233000</v>
       </c>
       <c r="AM3" t="n">
-        <v>95624000</v>
+        <v>-124971000</v>
       </c>
       <c r="AN3" t="n">
-        <v>60860000</v>
+        <v>406321000</v>
       </c>
       <c r="AO3" t="n">
-        <v>171064000</v>
+        <v>228924000</v>
       </c>
       <c r="AP3" t="n">
-        <v>14515000</v>
+        <v>31548000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>577171000</v>
+        <v>490029000</v>
       </c>
       <c r="AR3" t="n">
-        <v>182197000</v>
+        <v>131533000</v>
       </c>
       <c r="AS3" t="n">
-        <v>394974000</v>
+        <v>358496000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-2754000</v>
+        <v>-10644000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-25321000</v>
+        <v>-34665000</v>
       </c>
       <c r="AV3" t="n">
-        <v>384474000</v>
+        <v>863540000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>870430000</v>
+        <v>469057000</v>
       </c>
       <c r="C4" t="n">
-        <v>-13100444000</v>
+        <v>-14446154000</v>
       </c>
       <c r="D4" t="n">
-        <v>15060069000</v>
+        <v>13789609000</v>
       </c>
       <c r="E4" t="n">
-        <v>647230000</v>
+        <v>876660000</v>
       </c>
       <c r="F4" t="n">
-        <v>-283391000</v>
+        <v>-347730000</v>
       </c>
       <c r="G4" t="n">
+        <v>2361671000</v>
+      </c>
+      <c r="H4" t="n">
         <v>1635625000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2621741000</v>
-      </c>
       <c r="I4" t="n">
-        <v>15739000</v>
+        <v>2751000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1001855000</v>
+        <v>723295000</v>
       </c>
       <c r="K4" t="n">
-        <v>1327784000</v>
+        <v>-250293000</v>
       </c>
       <c r="L4" t="n">
-        <v>557000</v>
+        <v>1442000</v>
       </c>
       <c r="M4" t="n">
-        <v>-177463000</v>
+        <v>-181781000</v>
       </c>
       <c r="N4" t="n">
-        <v>-994706000</v>
+        <v>-169223000</v>
       </c>
       <c r="O4" t="n">
-        <v>-994706000</v>
+        <v>-169223000</v>
       </c>
       <c r="P4" t="n">
-        <v>647230000</v>
+        <v>876660000</v>
       </c>
       <c r="Q4" t="n">
-        <v>647230000</v>
+        <v>876660000</v>
       </c>
       <c r="R4" t="n">
-        <v>1959625000</v>
+        <v>-656545000</v>
       </c>
       <c r="S4" t="n">
-        <v>1959625000</v>
+        <v>-656545000</v>
       </c>
       <c r="T4" t="n">
-        <v>-13100444000</v>
+        <v>-14446154000</v>
       </c>
       <c r="U4" t="n">
-        <v>15060069000</v>
+        <v>13789609000</v>
       </c>
       <c r="V4" t="n">
-        <v>-3483460000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-31265000</v>
-      </c>
+        <v>156801000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>40054000</v>
+        <v>86356000</v>
       </c>
       <c r="Y4" t="n">
-        <v>47892000</v>
+        <v>23122000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-712696000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>-712696000</v>
-      </c>
+        <v>150791000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>150791000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-2701463000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2701463000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-125982000</v>
+        <v>-103468000</v>
       </c>
       <c r="AF4" t="n">
-        <v>157409000</v>
+        <v>244262000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-283391000</v>
+        <v>-347730000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1153821000</v>
+        <v>816787000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-472191000</v>
+        <v>-217992000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67078000</v>
+        <v>-139164000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-166039000</v>
+        <v>-47710000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-48233000</v>
+        <v>-247938000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-124971000</v>
+        <v>95624000</v>
       </c>
       <c r="AN4" t="n">
-        <v>406321000</v>
+        <v>60860000</v>
       </c>
       <c r="AO4" t="n">
-        <v>228924000</v>
+        <v>171064000</v>
       </c>
       <c r="AP4" t="n">
-        <v>31548000</v>
+        <v>14515000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>490029000</v>
+        <v>577171000</v>
       </c>
       <c r="AR4" t="n">
-        <v>131533000</v>
+        <v>182197000</v>
       </c>
       <c r="AS4" t="n">
-        <v>358496000</v>
+        <v>394974000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-10644000</v>
+        <v>-2754000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-34665000</v>
+        <v>-25321000</v>
       </c>
       <c r="AV4" t="n">
-        <v>863540000</v>
+        <v>384474000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1449063000</v>
+        <v>753744000</v>
       </c>
       <c r="C5" t="n">
-        <v>-8166627000</v>
+        <v>-8631529000</v>
       </c>
       <c r="D5" t="n">
-        <v>8483368000</v>
+        <v>7603056000</v>
       </c>
       <c r="E5" t="n">
-        <v>11104000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-362858000</v>
+        <v>-110911000</v>
       </c>
       <c r="G5" t="n">
-        <v>2621741000</v>
+        <v>2644539000</v>
       </c>
       <c r="H5" t="n">
-        <v>2538030000</v>
+        <v>2361671000</v>
       </c>
       <c r="I5" t="n">
-        <v>-28658000</v>
+        <v>-78000</v>
       </c>
       <c r="J5" t="n">
-        <v>112369000</v>
+        <v>282946000</v>
       </c>
       <c r="K5" t="n">
-        <v>-317494000</v>
+        <v>-1312183000</v>
       </c>
       <c r="L5" t="n">
-        <v>16787000</v>
+        <v>6532000</v>
       </c>
       <c r="M5" t="n">
-        <v>-133250000</v>
+        <v>-149051000</v>
       </c>
       <c r="N5" t="n">
-        <v>-460916000</v>
+        <v>-44426000</v>
       </c>
       <c r="O5" t="n">
-        <v>-460916000</v>
+        <v>-44426000</v>
       </c>
       <c r="P5" t="n">
-        <v>11104000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11104000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>316741000</v>
+        <v>-1028473000</v>
       </c>
       <c r="S5" t="n">
-        <v>316741000</v>
+        <v>-1028473000</v>
       </c>
       <c r="T5" t="n">
-        <v>-8166627000</v>
+        <v>-8631529000</v>
       </c>
       <c r="U5" t="n">
-        <v>8483368000</v>
+        <v>7603056000</v>
       </c>
       <c r="V5" t="n">
-        <v>-1382058000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-618379000</v>
-      </c>
+        <v>730474000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>21363000</v>
+        <v>131839000</v>
       </c>
       <c r="Y5" t="n">
-        <v>42425000</v>
+        <v>21008000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-613335000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-613335000</v>
-      </c>
+        <v>549905000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>549905000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-214132000</v>
+        <v>27722000</v>
       </c>
       <c r="AF5" t="n">
-        <v>148726000</v>
+        <v>138633000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-362858000</v>
+        <v>-110911000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1811921000</v>
+        <v>864655000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-377848000</v>
+        <v>-232469000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>276278000</v>
+        <v>106076000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-207483000</v>
+        <v>-1130826000</v>
       </c>
       <c r="AL5" t="n">
-        <v>513420000</v>
+        <v>1183912000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190700000</v>
+        <v>157274000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-220359000</v>
+        <v>-104284000</v>
       </c>
       <c r="AO5" t="n">
-        <v>82603000</v>
+        <v>124133000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4130000</v>
+        <v>5892000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>287353000</v>
+        <v>554692000</v>
       </c>
       <c r="AR5" t="n">
-        <v>18802000</v>
+        <v>179607000</v>
       </c>
       <c r="AS5" t="n">
-        <v>268551000</v>
+        <v>375085000</v>
       </c>
       <c r="AT5" t="n">
-        <v>22310000</v>
+        <v>78000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-47649000</v>
+        <v>5253000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1612763000</v>
+        <v>-2634517000</v>
       </c>
     </row>
   </sheetData>
@@ -3198,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EY2"/>
+  <dimension ref="A1:EW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3624,355 +3624,345 @@
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>hasPrePostMarketData</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
       <c r="EW1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4054,7 +4044,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Fan  Ye', 'age': 53, 'title': 'Founder &amp; Chairman', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 4671994, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tao  Ye', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 6266009, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Liuyu  Luo', 'age': 41, 'title': 'VP of Human Resources &amp; Administration and Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 1183927, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Yuan', 'age': 44, 'title': 'Financial Controller', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Tang', 'age': 42, 'title': 'Vice President of Sales &amp; Marketing', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Charmayne  Chan C.S., CGP', 'age': 41, 'title': 'Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Winny  Ye', 'title': 'Director of Investment Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Fan  Ye', 'age': 53, 'title': 'Founder &amp; Chairman', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 4668271, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tao  Ye', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 6261016, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Liuyu  Luo', 'age': 41, 'title': 'VP of Human Resources &amp; Administration and Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 1182984, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Yuan', 'age': 44, 'title': 'Financial Controller', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Tang', 'age': 42, 'title': 'Vice President of Sales &amp; Marketing', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Charmayne  Chan C.S., CGP', 'age': 41, 'title': 'Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Winny  Ye', 'title': 'Director of Investment Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4072,34 +4062,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="V2" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="AC2" t="n">
         <v>0.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.46</v>
+        <v>6.82</v>
       </c>
       <c r="AE2" t="n">
         <v>1788393600</v>
@@ -4111,31 +4101,31 @@
         <v>3.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.433</v>
+        <v>1.371</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.192616</v>
+        <v>1.755024</v>
       </c>
       <c r="AJ2" t="n">
-        <v>452000</v>
+        <v>128450</v>
       </c>
       <c r="AK2" t="n">
-        <v>452000</v>
+        <v>128450</v>
       </c>
       <c r="AL2" t="n">
-        <v>1107561</v>
+        <v>1033833</v>
       </c>
       <c r="AM2" t="n">
-        <v>1871375</v>
+        <v>960066</v>
       </c>
       <c r="AN2" t="n">
-        <v>1871375</v>
+        <v>960066</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4144,37 +4134,37 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>942372992</v>
+        <v>753898432</v>
       </c>
       <c r="AT2" t="n">
-        <v>942373040</v>
+        <v>740435960</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AW2" t="n">
         <v>48.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.047064696</v>
+        <v>0.03765176</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.097</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.50495</v>
+        <v>1.4153</v>
       </c>
       <c r="BB2" t="n">
         <v>0.034</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.048571434</v>
+        <v>0.061818182</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4185,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>2324465920</v>
+        <v>2135991424</v>
       </c>
       <c r="BG2" t="n">
         <v>-0.03771</v>
@@ -4200,16 +4190,16 @@
         <v>0.5250899999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.27301002</v>
+        <v>0.21966</v>
       </c>
       <c r="BL2" t="n">
         <v>1346247201</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.7345861</v>
+        <v>1.7385465</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.40355447</v>
+        <v>0.32210815</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4227,19 +4217,19 @@
         <v>-0.65</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.31925336</v>
+        <v>0.31908396</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.116</v>
+        <v>0.107</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.138</v>
+        <v>4.721</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.6666666</v>
+        <v>-0.7380952</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0337</v>
@@ -4253,273 +4243,265 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.241504</v>
+        <v>2.2382145</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.5151873</v>
+        <v>1.5129635</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.9055681</v>
+        <v>1.9027715</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.9600129</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>1.66667</v>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
+        <v>1.9571365</v>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CH2" t="n">
+        <v>3</v>
       </c>
       <c r="CI2" t="n">
-        <v>3</v>
+        <v>927990016</v>
       </c>
       <c r="CJ2" t="n">
-        <v>927990016</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.6889999999999999</v>
+        <v>452428992</v>
       </c>
       <c r="CL2" t="n">
-        <v>452428992</v>
+        <v>2195094016</v>
       </c>
       <c r="CM2" t="n">
-        <v>2195094016</v>
+        <v>0.573</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.573</v>
+        <v>1.172</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.172</v>
+        <v>20022927360</v>
       </c>
       <c r="CP2" t="n">
-        <v>20022927360</v>
+        <v>102.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>102.77</v>
+        <v>14.873</v>
       </c>
       <c r="CR2" t="n">
-        <v>14.873</v>
+        <v>0.01361</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.01361</v>
+        <v>-0.29611</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.29611</v>
+        <v>1148780032</v>
       </c>
       <c r="CU2" t="n">
-        <v>1148780032</v>
+        <v>293916512</v>
       </c>
       <c r="CV2" t="n">
-        <v>293916512</v>
+        <v>482276000</v>
       </c>
       <c r="CW2" t="n">
-        <v>482276000</v>
+        <v>-0.14</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.14</v>
+        <v>0.05737</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.05737</v>
+        <v>0.0226</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0226</v>
-      </c>
-      <c r="DA2" t="n">
         <v>0.02113</v>
       </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>1268.HK</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>1268.HK</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DH2" t="b">
+      <c r="DG2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1386207000000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.00999999</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>0.56 - 0.6</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>1033833</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.037037</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0.54 - 2.36</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.7627119</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-73.80952499999999</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.31908396</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.11934</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>MEIDONG AUTO</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_251962529</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>4.6924753</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.3326</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.3726193</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.8552999999999999</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.60432416</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ER2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>China MeiDong Auto Holdings Limited</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DL2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_251962529</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>5.865594</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.397</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.3618961</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.80495006</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.5348683</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>1.7 - Buy</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>China MeiDong Auto Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>MEIDONG AUTO</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1386207000000</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>0.67 - 0.85</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>1107561</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.060000002</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.09375000999999999</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>0.64 - 2.38</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>-1.6800001</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.7058824</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-66.666664</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="EU2" t="b">
-        <v>1</v>
+      <c r="EU2" t="n">
+        <v>1.8181801</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>0.31925336</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>0.11934</v>
-      </c>
-      <c r="EY2" t="inlineStr"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="EW2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
